--- a/docs/培训/OpenWorker培训/01-质量周报/不良品处理单.xlsx
+++ b/docs/培训/OpenWorker培训/01-质量周报/不良品处理单.xlsx
@@ -507,11 +507,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NCR-39-01</t>
+          <t>NCR-40-01</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -565,11 +565,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NCR-39-02</t>
+          <t>NCR-40-02</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46287</v>
+        <v>46294</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -623,11 +623,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NCR-39-03</t>
+          <t>NCR-40-03</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46287</v>
+        <v>46294</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -681,11 +681,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NCR-39-04</t>
+          <t>NCR-40-04</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46288</v>
+        <v>46295</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -739,11 +739,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NCR-39-05</t>
+          <t>NCR-40-05</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46289</v>
+        <v>46296</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -797,11 +797,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NCR-39-06</t>
+          <t>NCR-40-06</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46289</v>
+        <v>46296</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NCR-39-07</t>
+          <t>NCR-40-07</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46290</v>
+        <v>46297</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -913,11 +913,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NCR-39-08</t>
+          <t>NCR-40-08</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46290</v>
+        <v>46297</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
